--- a/artfynd/A 59358-2022 artfynd.xlsx
+++ b/artfynd/A 59358-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 59358-2022 artfynd.xlsx
+++ b/artfynd/A 59358-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>106579022</v>
       </c>
       <c r="B2" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>812440.5708999278</v>
+        <v>812441</v>
       </c>
       <c r="R2" t="n">
-        <v>7325994.600107014</v>
+        <v>7325995</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -804,49 +799,44 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109933667</v>
+        <v>109933678</v>
       </c>
       <c r="B3" t="n">
-        <v>56779</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56925</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103037</v>
+        <v>100045</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Sångsvan</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Cygnus cygnus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -856,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>812440.5708999278</v>
+        <v>812441</v>
       </c>
       <c r="R3" t="n">
-        <v>7325994.600107014</v>
+        <v>7325995</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -902,6 +892,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På åker.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,49 +923,44 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109933693</v>
+        <v>109933673</v>
       </c>
       <c r="B4" t="n">
-        <v>57000</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103051</v>
+        <v>100065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenfink</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carpodacus erythrinus</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -980,10 +970,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>812440.5708999278</v>
+        <v>812441</v>
       </c>
       <c r="R4" t="n">
-        <v>7325994.600107014</v>
+        <v>7325995</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1028,6 +1018,11 @@
           <t>08:50</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På åker.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1049,6 +1044,244 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>109933667</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Inbyn NO Boden, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>812441</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7325995</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>109933693</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58586</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103051</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rosenfink</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Carpodacus erythrinus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pallas, 1770)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Inbyn NO Boden, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>812441</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7325995</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Mats Bergquist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 59358-2022 artfynd.xlsx
+++ b/artfynd/A 59358-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106579022</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109933678</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1044,6 +1059,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109933673</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1163,6 +1183,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109933667</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1282,8 +1307,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109933693</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>